--- a/product_upload/packages/18/file.xlsx
+++ b/product_upload/packages/18/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -840,6 +845,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>BETNOVATE-C OINT.</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-B65560674405</t>
         </is>
       </c>
@@ -863,7 +873,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1030,6 +1040,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>BETNOVATE-C CREAM</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-86ABD71A8083</t>
         </is>
       </c>
@@ -1053,7 +1068,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1216,6 +1231,11 @@
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>BETNOVATE OINTMENT 0.1%</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-B8CCA9D28E93</t>
         </is>
       </c>
@@ -1239,7 +1259,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1402,6 +1422,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>BETNOVATE CREAM 0.1%</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-E952400D6B25</t>
         </is>
       </c>
@@ -1425,7 +1450,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1598,6 +1623,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>BETNOVATE 0.1% SCALP APPLICATION</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-381D93F5FCE4</t>
         </is>
       </c>
@@ -1621,7 +1651,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1792,6 +1822,11 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>BETAZOL</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-847AC8FD134A</t>
         </is>
       </c>
@@ -1815,7 +1850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1990,6 +2025,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>BILTRICIDE 600MG TABS</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-401CAA83A384</t>
         </is>
       </c>
@@ -2013,7 +2053,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2180,6 +2220,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>BLOPRESS 16 PLUS TABLETS</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-1F37D835EB92</t>
         </is>
       </c>
@@ -2203,7 +2248,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2370,6 +2415,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>BLOPRESS 16 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-1A10676BB17F</t>
         </is>
       </c>
@@ -2393,7 +2443,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2548,6 +2598,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>BISOLVON ELIXIR 4MG-5ML</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-B166ECFC1444</t>
         </is>
       </c>
@@ -2571,7 +2626,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2738,6 +2793,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>BISOLVON 8MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-B076E5A9F3AB</t>
         </is>
       </c>
@@ -2761,7 +2821,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2932,6 +2992,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>BLOPRESS 8MG TAB.</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-13A16660692E</t>
         </is>
       </c>
@@ -2955,7 +3020,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3130,6 +3195,11 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>BISCOR 5MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-0E9FD4FA3A12</t>
         </is>
       </c>
@@ -3153,7 +3223,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3312,6 +3382,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>BIOCEF 500MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-336F82C8D200</t>
         </is>
       </c>
@@ -3335,7 +3410,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3510,6 +3585,11 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>BISCOR 10MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-2D3A4D108020</t>
         </is>
       </c>
@@ -3533,7 +3613,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3702,6 +3782,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>CADUET 5-20</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-3219E397B01D</t>
         </is>
       </c>
@@ -3725,7 +3810,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3884,6 +3969,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>CAPRIL 50MG TAB</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-66E4B3E5CCBC</t>
         </is>
       </c>
@@ -3907,7 +3997,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4066,6 +4156,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>CAPRIL 25MG TAB</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-A3296FE03FA3</t>
         </is>
       </c>
@@ -4089,7 +4184,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4248,6 +4343,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>CARVIDOL 25 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-CC0A8DA100D2</t>
         </is>
       </c>
@@ -4271,7 +4371,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4442,6 +4542,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>CARDURA XL 4 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-F4788C6BE9A5</t>
         </is>
       </c>
@@ -4465,7 +4570,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4628,6 +4733,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>CARDURA 4 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-9978F9BD28AC</t>
         </is>
       </c>
@@ -4651,7 +4761,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4806,6 +4916,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>CARDIOPROL 5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-D8C9A550FA53</t>
         </is>
       </c>
@@ -4829,7 +4944,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4984,6 +5099,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>CARDIOPROL 10MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-207D9C67C67E</t>
         </is>
       </c>
@@ -5007,7 +5127,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5162,6 +5282,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>CARDICOR PLUS 5/12.5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-9F8E6F152536</t>
         </is>
       </c>
@@ -5185,7 +5310,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5352,6 +5477,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>CARDICOR 5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-310DA7799273</t>
         </is>
       </c>
@@ -5375,7 +5505,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5538,6 +5668,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>CARDICOR 2.5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-4C82261E79E0</t>
         </is>
       </c>
@@ -5561,7 +5696,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5728,6 +5863,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>CARDICOR 10MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-C3BD868E8DFE</t>
         </is>
       </c>
@@ -5751,7 +5891,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5916,6 +6056,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>CADUET 5-40</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-CBE3F4B1DC00</t>
         </is>
       </c>
@@ -5939,7 +6084,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6090,6 +6235,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>CANDRIL SACHETS</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-FA267A72170D</t>
         </is>
       </c>
@@ -6113,7 +6263,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6276,6 +6426,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>CALCIUM CHLORIDE 7.35% INJECTION</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-D9040A776EA7</t>
         </is>
       </c>
@@ -6299,7 +6454,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6466,6 +6621,11 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>CALCIUM CHLORIDE 7.35% INJECTION</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-8A4FAFB2F404</t>
         </is>
       </c>
@@ -6489,7 +6649,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6656,6 +6816,11 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>CALCIUM CHLORIDE 7.35% INJECTION</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-5808E5F3C2F2</t>
         </is>
       </c>
@@ -6679,7 +6844,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6846,6 +7011,11 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>CALCINATE</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-8830AEEE7EAA</t>
         </is>
       </c>
@@ -6869,7 +7039,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7032,6 +7202,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>CALAZOL CREAM</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-68C5B42261EB</t>
         </is>
       </c>
@@ -7055,7 +7230,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7222,6 +7397,11 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>CAFERGOT 1 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-1B35FF0C4B69</t>
         </is>
       </c>
@@ -7245,7 +7425,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7408,6 +7588,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>CANDIZOLE 2% VAGINAL CREAM</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-2085461750A5</t>
         </is>
       </c>
@@ -7431,7 +7616,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7598,6 +7783,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>CANDIVAST 50MG CAP</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-3466CC9B0D63</t>
         </is>
       </c>
@@ -7621,7 +7811,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7788,6 +7978,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>CANDIVAST 150MG CAP</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-9683C4FE1493</t>
         </is>
       </c>
@@ -7811,7 +8006,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7966,6 +8161,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>CANDEUR 50MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-7310BD847FA0</t>
         </is>
       </c>
@@ -7989,7 +8189,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8152,6 +8352,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>CANDEUR 200MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-A633D1944FD1</t>
         </is>
       </c>
@@ -8175,7 +8380,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8338,6 +8543,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>CANDEUR 150MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-DDC5B4696EE9</t>
         </is>
       </c>
@@ -8361,7 +8571,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8516,6 +8726,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>CANDRIL SACHETS</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-42DF9E4A77F3</t>
         </is>
       </c>
@@ -8539,7 +8754,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8706,6 +8921,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>CalSource Ca-C1000</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-89A8AA153233</t>
         </is>
       </c>
@@ -8729,7 +8949,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8900,6 +9120,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>CALCIUM SANDOZ EFF TAB FORTE</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-C02DBF9A0164</t>
         </is>
       </c>
@@ -8923,7 +9148,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9094,6 +9319,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>CALSYR  SYRUP</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-22760C0ABF47</t>
         </is>
       </c>
@@ -9117,7 +9347,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9284,6 +9514,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>AZI-ONCE</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-9B468CC6C8A1</t>
         </is>
       </c>
@@ -9307,7 +9542,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9474,6 +9709,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>AZI-ONCE</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-6D73B2C31375</t>
         </is>
       </c>
@@ -9497,7 +9737,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9660,6 +9900,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>AZI-ONCE</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-D64B9BD47A85</t>
         </is>
       </c>
@@ -9683,7 +9928,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9854,6 +10099,11 @@
       </c>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>AZI-ONCE</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-5610B3BBAB32</t>
         </is>
       </c>
@@ -9877,7 +10127,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10048,6 +10298,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>AZIMAC 500 mg</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-F3D912BBDC29</t>
         </is>
       </c>
@@ -10071,7 +10326,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10238,6 +10493,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>AZIMAC 250 mg</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-B5D217743CA7</t>
         </is>
       </c>
@@ -10261,7 +10521,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10424,6 +10684,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>AVOTIN- A</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-075D39629C2A</t>
         </is>
       </c>
@@ -10447,7 +10712,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10606,6 +10871,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>AVORAL 2% SHAMPOO</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-A15DE1B68179</t>
         </is>
       </c>
@@ -10629,7 +10899,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10796,6 +11066,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>AVOQUIN</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-D67C47D9486A</t>
         </is>
       </c>
@@ -10819,7 +11094,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10990,6 +11265,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>AVOMACK</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-62E052574E9B</t>
         </is>
       </c>
@@ -11013,7 +11293,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11176,6 +11456,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>AVOMACK</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-365328867DFE</t>
         </is>
       </c>
@@ -11199,7 +11484,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11370,6 +11655,11 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>Avocom-M Cream</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-38D26977171B</t>
         </is>
       </c>
@@ -11393,7 +11683,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11556,6 +11846,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>Avocom-M Cream</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-A453F7275E1E</t>
         </is>
       </c>
@@ -11579,7 +11874,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11738,6 +12033,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>AVOGAIN</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-D1A55D769D14</t>
         </is>
       </c>
@@ -11761,7 +12061,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11924,6 +12224,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>BALAD</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-85D32C4E59D9</t>
         </is>
       </c>
@@ -11947,7 +12252,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12110,6 +12415,11 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>BACTROBAN OINT 2%</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-55A7DF16AC54</t>
         </is>
       </c>
@@ -12133,7 +12443,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12292,6 +12602,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>BACTROBAN NASAL OINTMENT 2%</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-5DB13E117784</t>
         </is>
       </c>
@@ -12315,7 +12630,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12474,6 +12789,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>BACTRIM SUSP</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-69BA621CEAFA</t>
         </is>
       </c>
@@ -12497,7 +12817,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12652,6 +12972,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>AVOGAIN</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-7812FCBBEC8E</t>
         </is>
       </c>
@@ -12675,7 +13000,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12838,6 +13163,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>BACTALL 500MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-4C26506701F5</t>
         </is>
       </c>
@@ -12861,7 +13191,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13020,6 +13350,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>BACTALL 250MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-D3016859258B</t>
         </is>
       </c>
@@ -13043,7 +13378,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13210,6 +13545,11 @@
       </c>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>BABYLYTE ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-EFE7AE81FE37</t>
         </is>
       </c>
@@ -13233,7 +13573,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13388,6 +13728,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>BABYLYTE</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-126BAA6B909A</t>
         </is>
       </c>
@@ -13411,7 +13756,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13570,6 +13915,11 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>BABYLYTE</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-7016DBA419F9</t>
         </is>
       </c>
@@ -13593,7 +13943,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13752,6 +14102,11 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>BABYLYTE</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-42922D843D23</t>
         </is>
       </c>
@@ -13775,7 +14130,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13946,6 +14301,11 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>BACTRIM FORTE TAB</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-70FE7B510F06</t>
         </is>
       </c>
@@ -13969,7 +14329,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14134,6 +14494,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>AVODART 0.5MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-3D4EB8EBF95C</t>
         </is>
       </c>
@@ -14157,7 +14522,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14324,6 +14689,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>AVOCOM</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-AE590B78C665</t>
         </is>
       </c>
@@ -14347,7 +14717,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14520,6 +14890,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>AUGMENTIN 457MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-502C05C83945</t>
         </is>
       </c>
@@ -14543,7 +14918,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14708,6 +15083,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>AUGMENTIN 312 MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-57C332766CB1</t>
         </is>
       </c>
@@ -14731,7 +15111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14900,6 +15280,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>AUGMENTIN 228 MG-5ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-A7C8CC664D64</t>
         </is>
       </c>
@@ -14923,7 +15308,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15088,6 +15473,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>AUGMENTIN 156 Mg-5 ML SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-F93A33193333</t>
         </is>
       </c>
@@ -15111,7 +15501,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15280,6 +15670,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>AUGMENTIN 1 G TAB</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-818AD660D475</t>
         </is>
       </c>
@@ -15303,7 +15698,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15472,6 +15867,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>AUGMENTIN ES SUSPENSION</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-2321DEA77F2F</t>
         </is>
       </c>
@@ -15495,7 +15895,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15664,6 +16064,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>AUGMENTIN 625 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-CCFE9F577876</t>
         </is>
       </c>
@@ -15687,7 +16092,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15854,6 +16259,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>AVOCOM</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-10CDF397D001</t>
         </is>
       </c>
@@ -15877,7 +16287,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16048,6 +16458,11 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>AVOCIN</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-BB66BA2ABD9C</t>
         </is>
       </c>
@@ -16071,7 +16486,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16226,6 +16641,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>AVOCIN</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-932C62D53CFB</t>
         </is>
       </c>
@@ -16249,7 +16669,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16420,6 +16840,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>AVOBAN 2% W-W OINTMENT</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-9E1E188CB1DB</t>
         </is>
       </c>
@@ -16443,7 +16868,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16610,6 +17035,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>AVAXIM 80U-0.5ML PEDIATRIC VACCINE</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-D8032FDB543D</t>
         </is>
       </c>
@@ -16633,7 +17063,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16800,6 +17230,11 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>AVAXIM 160 UNITS VACCINE S.D SYRINGE</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-098BF4501B8E</t>
         </is>
       </c>
@@ -16823,7 +17258,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16994,6 +17429,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>AVOCOM 0.05% AQUEOUS NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-F1C5035B5E0C</t>
         </is>
       </c>
@@ -17017,7 +17457,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17186,6 +17626,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>AVALOX 400MG TAB</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-ADA71B8A089F</t>
         </is>
       </c>
@@ -17209,7 +17654,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17374,6 +17819,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>AVALOX 400MG TAB</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-D6953A20BC73</t>
         </is>
       </c>
@@ -17397,7 +17847,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17568,6 +18018,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>AVALON AVOCAINE</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-78AFB9DEE3CF</t>
         </is>
       </c>
@@ -17591,7 +18046,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17754,6 +18209,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>AURORIX 300MG TAB</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-696D03FBF7A3</t>
         </is>
       </c>
@@ -17777,7 +18237,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17940,6 +18400,11 @@
       </c>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>AURORIX 150MG TAB</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-D1C21694472A</t>
         </is>
       </c>
@@ -17963,7 +18428,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18136,6 +18601,11 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>AUGMENTIN TAB 375 MG</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-B0A42151FCC0</t>
         </is>
       </c>
@@ -18159,7 +18629,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18328,6 +18798,11 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>AVAMYS SUSPENSION FOR NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-BC7D2639EEE4</t>
         </is>
       </c>
@@ -18351,7 +18826,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18510,6 +18985,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>BALANCED SALT SOLUTION BOTTLE</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-C5C949123FAA</t>
         </is>
       </c>
@@ -18533,7 +19013,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18696,6 +19176,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>BETADERM 0.1% cream</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-AEE7707AB552</t>
         </is>
       </c>
@@ -18719,7 +19204,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18886,6 +19371,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>BERTIGO 8 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-2F3576197860</t>
         </is>
       </c>
@@ -18909,7 +19399,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19080,6 +19570,11 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>BERTIGO 24 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-59A03B1D8EDE</t>
         </is>
       </c>
@@ -19103,7 +19598,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19274,6 +19769,11 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>BERTIGO 16 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-8F8EFE085F13</t>
         </is>
       </c>
@@ -19297,7 +19797,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19455,6 +19955,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>BENZAL 25% LOTION</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-B7CAD06EB7D8</t>
         </is>
@@ -19471,7 +19976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19517,100 +20022,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19642,7 +20152,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19657,92 +20167,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-25424</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>131.71</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>97</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19774,7 +20289,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19789,92 +20304,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-10617</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>101.17</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>98</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19906,7 +20426,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19921,92 +20441,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-46450</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>173.94</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Home Health Test</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>99</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20038,7 +20563,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20053,92 +20578,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-91122</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>272.68</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Home Health Test</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>100</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20170,7 +20700,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20185,92 +20715,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-43163</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>165.24</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Home Health Test</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>101</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20302,7 +20837,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20317,92 +20852,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-29693</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>275.86</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>102</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20434,7 +20974,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20449,92 +20989,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-27082</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>329.68</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>103</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20566,7 +21111,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20581,92 +21126,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-57086</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>28.5</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>104</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20698,7 +21248,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20713,92 +21263,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-29118</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>452.27</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Thermometer</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>105</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20830,7 +21385,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20845,92 +21400,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-69256</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>45.35</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Wheelchairs &amp; Scooters</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>106</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20962,7 +21522,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20977,92 +21537,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-75474</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>245.39</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>107</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21094,7 +21659,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -21109,92 +21674,97 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>SKU-71670</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>224.75</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T13" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U13" t="inlineStr">
+      <c r="U13" t="n">
+        <v>108</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W13" t="n">
+      <c r="X13" t="n">
         <v>100</v>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y13" t="n">
+      <c r="Z13" t="n">
         <v>12</v>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21211,7 +21781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21317,6 +21887,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21352,7 +21932,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21417,6 +21997,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-968E4D80BA9E</t>
         </is>
@@ -21453,7 +22043,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21518,6 +22108,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-D44897C6C760</t>
         </is>
@@ -21554,7 +22154,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21619,6 +22219,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-D3A7EE21EE4E</t>
         </is>
@@ -21655,7 +22265,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21720,6 +22330,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-6363B05E5ED1</t>
         </is>
@@ -21756,7 +22376,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21821,6 +22441,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-0452B442509A</t>
         </is>
@@ -21857,7 +22487,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21922,6 +22552,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-BB4F0D2C938E</t>
         </is>
@@ -21958,7 +22598,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22023,6 +22663,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-3D23B48D5C97</t>
         </is>
@@ -22059,7 +22709,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22124,6 +22774,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-D686DDE9BE2C</t>
         </is>
@@ -22160,7 +22820,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22225,6 +22885,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-6B154F8BF3A3</t>
         </is>
@@ -22261,7 +22931,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22326,6 +22996,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-A491C17B3671</t>
         </is>
@@ -22362,7 +23042,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22427,6 +23107,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-87E8F179874F</t>
         </is>
@@ -22463,7 +23153,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22528,6 +23218,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-4AB26BFFD93D</t>
         </is>
@@ -22564,7 +23264,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22629,6 +23329,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-2B442B026005</t>
         </is>
@@ -22665,7 +23375,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22730,6 +23440,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-BA9D3D4D6A02</t>
         </is>
@@ -22766,7 +23486,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22831,6 +23551,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-A66E2D514FCA</t>
         </is>
@@ -22867,7 +23597,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22932,6 +23662,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-9529BD2AA5D7</t>
         </is>
@@ -22968,7 +23708,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23033,6 +23773,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-79C3135E47CA</t>
         </is>
@@ -23069,7 +23819,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23134,6 +23884,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-CB091518A2EE</t>
         </is>
@@ -23170,7 +23930,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23235,6 +23995,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-CE7149A89528</t>
         </is>
@@ -23271,7 +24041,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23336,6 +24106,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-0AF1B6714BED</t>
         </is>

--- a/product_upload/packages/18/file.xlsx
+++ b/product_upload/packages/18/file.xlsx
@@ -2451,8 +2451,16 @@
           <t>8045974058-963-318679920689</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BISOLVON ELIXIR 4MG-5ML</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>BISOLVON ELIXIR 4MG-5ML detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -3231,8 +3239,16 @@
           <t>3540859207-912-530066902295</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BIOCEF 500MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>BIOCEF 500MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3818,8 +3834,16 @@
           <t>7864941285-012-024185511849</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CAPRIL 50MG TAB</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>CAPRIL 50MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -4005,8 +4029,16 @@
           <t>8258159304-193-414952051648</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CAPRIL 25MG TAB</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>CAPRIL 25MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4192,8 +4224,16 @@
           <t>2089807621-218-757406282356</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CARVIDOL 25 MG TAB</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>CARVIDOL 25 MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4578,8 +4618,16 @@
           <t>8755098156-994-003747578517</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CARDURA 4 mg tablet</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>CARDURA 4 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4769,8 +4817,16 @@
           <t>4447269211-911-745864405280</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CARDIOPROL 5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>CARDIOPROL 5MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -4952,8 +5008,16 @@
           <t>4326411559-922-479157963178</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CARDIOPROL 10MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>CARDIOPROL 10MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -5135,8 +5199,16 @@
           <t>2783123519-370-059276285254</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CARDICOR PLUS 5/12.5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>CARDICOR PLUS 5/12.5MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5899,8 +5971,16 @@
           <t>3822120204-384-615183302946</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CADUET 5-40</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>CADUET 5-40 detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>PFIZER SAUDI LIMITED</t>
@@ -6092,8 +6172,16 @@
           <t>3698926167-974-669754565180</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CANDRIL SACHETS</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>CANDRIL SACHETS detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6271,8 +6359,16 @@
           <t>4629191088-928-678954145110</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CALCIUM CHLORIDE 7.35% INJECTION</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>CALCIUM CHLORIDE 7.35% INJECTION detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6462,8 +6558,16 @@
           <t>7526275982-519-262808144290</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CALCIUM CHLORIDE 7.35% INJECTION</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>CALCIUM CHLORIDE 7.35% INJECTION detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6657,8 +6761,16 @@
           <t>1443027781-870-507731168337</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CALCIUM CHLORIDE 7.35% INJECTION</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>CALCIUM CHLORIDE 7.35% INJECTION detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6852,8 +6964,16 @@
           <t>0060525295-557-467506205351</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CALCINATE</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>CALCINATE detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -7047,8 +7167,16 @@
           <t>7893251155-920-289758978026</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CALAZOL CREAM</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>CALAZOL CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7433,8 +7561,16 @@
           <t>9773068315-648-642547666004</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CANDIZOLE 2% VAGINAL CREAM</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>CANDIZOLE 2% VAGINAL CREAM detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -8014,8 +8150,16 @@
           <t>8498637490-272-539128033482</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CANDEUR 50MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>CANDEUR 50MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -8197,8 +8341,16 @@
           <t>2353385424-424-004656612156</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CANDEUR 200MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>CANDEUR 200MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8388,8 +8540,16 @@
           <t>5937355101-293-739190092278</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CANDEUR 150MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>CANDEUR 150MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8579,8 +8739,16 @@
           <t>6080903976-321-721989947828</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CANDRIL SACHETS</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>CANDRIL SACHETS detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -10720,8 +10888,16 @@
           <t>0919294527-724-984914988017</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AVORAL 2% SHAMPOO</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>AVORAL 2% SHAMPOO detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -11882,8 +12058,16 @@
           <t>5345581873-118-398014612365</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AVOGAIN</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>AVOGAIN detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -12069,8 +12253,16 @@
           <t>1678890304-388-827403214099</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BALAD</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>BALAD detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12260,8 +12452,16 @@
           <t>6688282922-326-347972794047</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BACTROBAN OINT 2%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>BACTROBAN OINT 2% detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12451,8 +12651,16 @@
           <t>1346755228-742-189487972720</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BACTROBAN NASAL OINTMENT 2%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>BACTROBAN NASAL OINTMENT 2% detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12638,8 +12846,16 @@
           <t>0934589723-450-228175836185</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BACTRIM SUSP</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>BACTRIM SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12825,8 +13041,16 @@
           <t>0330927205-926-172031143036</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AVOGAIN</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>AVOGAIN detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -13008,8 +13232,16 @@
           <t>7296858204-025-467341524102</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BACTALL 500MG TABLET</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>BACTALL 500MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13199,8 +13431,16 @@
           <t>3709915864-387-279944390252</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BACTALL 250MG TABLET</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>BACTALL 250MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13581,8 +13821,16 @@
           <t>6544342555-573-069695262305</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BABYLYTE</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>BABYLYTE detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13764,8 +14012,16 @@
           <t>7533291321-708-902413628817</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BABYLYTE</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>BABYLYTE detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -13951,8 +14207,16 @@
           <t>5947436484-881-201167650268</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BABYLYTE</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>BABYLYTE detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -16494,8 +16758,16 @@
           <t>6583009104-975-277607870253</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AVOCIN</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>AVOCIN detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -17071,8 +17343,16 @@
           <t>0751729622-298-964814752276</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AVAXIM 160 UNITS VACCINE S.D SYRINGE</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>AVAXIM 160 UNITS VACCINE S.D SYRINGE detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -17662,8 +17942,16 @@
           <t>6858651214-313-815741802981</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AVALOX 400MG TAB</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>AVALOX 400MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
           <t>DEEF PHARMACEUTICAL INDUSTRIES</t>
@@ -18054,8 +18342,16 @@
           <t>9365005376-704-534309325467</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AURORIX 300MG TAB</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>AURORIX 300MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -18245,8 +18541,16 @@
           <t>8021334118-701-968093268003</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AURORIX 150MG TAB</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>AURORIX 150MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -18834,8 +19138,16 @@
           <t>8912128456-246-369428482751</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BALANCED SALT SOLUTION BOTTLE</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>BALANCED SALT SOLUTION BOTTLE detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -19805,8 +20117,16 @@
           <t>0381761278-444-189016065241</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ BENZAL 25% LOTION</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>BENZAL 25% LOTION detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/18/file.xlsx
+++ b/product_upload/packages/18/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20342,7 +20342,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22101,7 +22101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22182,40 +22182,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22295,38 +22300,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>256.97</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-968E4D80BA9E</t>
         </is>
@@ -22406,38 +22416,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>202.3</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-D44897C6C760</t>
         </is>
@@ -22517,38 +22532,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>454.15</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-D3A7EE21EE4E</t>
         </is>
@@ -22628,38 +22648,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>193.41</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-6363B05E5ED1</t>
         </is>
@@ -22739,38 +22764,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>35.83</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-0452B442509A</t>
         </is>
@@ -22850,38 +22880,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>266.43</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-BB4F0D2C938E</t>
         </is>
@@ -22961,38 +22996,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>337.32</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-3D23B48D5C97</t>
         </is>
@@ -23072,38 +23112,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>337.82</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-D686DDE9BE2C</t>
         </is>
@@ -23183,38 +23228,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>483.11</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-6B154F8BF3A3</t>
         </is>
@@ -23294,38 +23344,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>20.47</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-A491C17B3671</t>
         </is>
@@ -23405,38 +23460,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>487.32</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-87E8F179874F</t>
         </is>
@@ -23516,38 +23576,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>387.56</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-4AB26BFFD93D</t>
         </is>
@@ -23627,38 +23692,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>185.46</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-2B442B026005</t>
         </is>
@@ -23738,38 +23808,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>337.75</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-BA9D3D4D6A02</t>
         </is>
@@ -23849,38 +23924,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>429</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-A66E2D514FCA</t>
         </is>
@@ -23960,38 +24040,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>121.1</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-9529BD2AA5D7</t>
         </is>
@@ -24071,38 +24156,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>425.41</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-79C3135E47CA</t>
         </is>
@@ -24182,38 +24272,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>325.77</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-CB091518A2EE</t>
         </is>
@@ -24293,38 +24388,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>159.36</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-CE7149A89528</t>
         </is>
@@ -24404,38 +24504,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>462.63</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-0AF1B6714BED</t>
         </is>
